--- a/2026/BRIN 3219/Septiembre/MinistroBrin3219-Septiembre.xlsx
+++ b/2026/BRIN 3219/Septiembre/MinistroBrin3219-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467293A8-4F86-437C-A8C3-FF68625EBB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC518EA-606C-44D7-A19E-93260F3F52DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1240,7 +1245,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1546,138 +1551,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="27" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1735,6 +1612,45 @@
     <xf numFmtId="165" fontId="17" fillId="14" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="17" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1747,11 +1663,95 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1832,9 +1832,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1872,9 +1872,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1907,9 +1907,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1942,9 +1959,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2119,21 +2153,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M117"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="43" t="s">
         <v>172</v>
@@ -2142,7 +2176,7 @@
       <c r="D1" s="43"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="45" t="s">
         <v>12</v>
@@ -2151,16 +2185,16 @@
       <c r="D2" s="45"/>
       <c r="E2" s="46"/>
     </row>
-    <row r="3" spans="1:5" ht="114.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="114.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="238" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="199"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="239"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -2171,7 +2205,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>168</v>
       </c>
@@ -2184,7 +2218,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>164</v>
       </c>
@@ -2195,57 +2229,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="201" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="241" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="201"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="201"/>
-      <c r="C9" s="201"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="201"/>
-      <c r="C10" s="201"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="200" t="s">
+      <c r="C8" s="241"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="240" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="200"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="200"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="200"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="200"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="200"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="200"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="200"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="240"/>
+      <c r="C13" s="240"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="240"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="240"/>
+      <c r="B14" s="240"/>
+      <c r="C14" s="240"/>
+      <c r="D14" s="240"/>
+      <c r="E14" s="240"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="240"/>
+      <c r="B15" s="240"/>
+      <c r="C15" s="240"/>
+      <c r="D15" s="240"/>
+      <c r="E15" s="240"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="240"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="240"/>
+      <c r="D16" s="240"/>
+      <c r="E16" s="240"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>149</v>
       </c>
@@ -2254,7 +2288,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>23</v>
       </c>
@@ -2263,23 +2297,23 @@
       <c r="D21" s="95"/>
       <c r="E21" s="90"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="194" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="236" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="195"/>
+      <c r="B22" s="237"/>
       <c r="C22" s="138"/>
-      <c r="D22" s="186">
+      <c r="D22" s="164">
         <v>442956.59</v>
       </c>
       <c r="E22" s="135"/>
       <c r="H22" s="80"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="194" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="236" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="195"/>
+      <c r="B23" s="237"/>
       <c r="C23" s="138"/>
       <c r="D23" s="164">
         <v>-69765.59</v>
@@ -2287,19 +2321,19 @@
       <c r="E23" s="91"/>
       <c r="H23" s="80"/>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="187" t="s">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="185" t="s">
         <v>141</v>
       </c>
       <c r="B24" s="145"/>
       <c r="C24" s="138"/>
-      <c r="D24" s="188">
+      <c r="D24" s="280">
         <v>24500</v>
       </c>
       <c r="E24" s="91"/>
       <c r="H24" s="80"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="139" t="s">
         <v>7</v>
       </c>
@@ -2311,48 +2345,48 @@
         <v>397691</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="245" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="201" t="s">
         <v>134</v>
       </c>
       <c r="B26" s="139"/>
       <c r="C26" s="139"/>
       <c r="D26" s="165"/>
-      <c r="E26" s="242"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E26" s="198"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="138" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="243"/>
-      <c r="C27" s="243"/>
-      <c r="D27" s="190">
+      <c r="B27" s="199"/>
+      <c r="C27" s="199"/>
+      <c r="D27" s="66">
         <v>55887.28</v>
       </c>
-      <c r="E27" s="244"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E27" s="200"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="138" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="243"/>
-      <c r="C28" s="243"/>
-      <c r="D28" s="190"/>
-      <c r="E28" s="244"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B28" s="199"/>
+      <c r="C28" s="199"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="200"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="139" t="s">
         <v>135</v>
       </c>
       <c r="B29" s="139"/>
       <c r="C29" s="139"/>
       <c r="D29" s="165"/>
-      <c r="E29" s="246">
+      <c r="E29" s="202">
         <f>SUM(D26:D28)</f>
         <v>55887.28</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="140" t="s">
         <v>15</v>
       </c>
@@ -2361,18 +2395,18 @@
       <c r="D30" s="166"/>
       <c r="E30" s="127"/>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="194" t="s">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="236" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="195"/>
+      <c r="B31" s="237"/>
       <c r="C31" s="141"/>
-      <c r="D31" s="185">
+      <c r="D31" s="92">
         <v>28834</v>
       </c>
       <c r="E31" s="93"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="139" t="s">
         <v>133</v>
       </c>
@@ -2384,7 +2418,7 @@
         <v>28834</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="140" t="s">
         <v>8</v>
       </c>
@@ -2393,40 +2427,40 @@
       <c r="D33" s="167"/>
       <c r="E33" s="128"/>
     </row>
-    <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="63" t="s">
         <v>131</v>
       </c>
       <c r="B34" s="63"/>
       <c r="C34" s="63"/>
-      <c r="D34" s="185">
+      <c r="D34" s="92">
         <v>1555264.54</v>
       </c>
       <c r="E34" s="93"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="63" t="s">
         <v>132</v>
       </c>
       <c r="B35" s="63"/>
       <c r="C35" s="63"/>
-      <c r="D35" s="185">
+      <c r="D35" s="92">
         <v>95000</v>
       </c>
       <c r="E35" s="135"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="63" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="143"/>
       <c r="C36" s="63"/>
-      <c r="D36" s="185">
+      <c r="D36" s="92">
         <v>88487.35</v>
       </c>
       <c r="E36" s="93"/>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="139" t="s">
         <v>1</v>
       </c>
@@ -2438,142 +2472,142 @@
         <v>1738751.8900000001</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="140"/>
       <c r="B38" s="139"/>
       <c r="C38" s="139"/>
       <c r="D38" s="165"/>
       <c r="E38" s="130"/>
     </row>
-    <row r="39" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="138" t="s">
         <v>119</v>
       </c>
       <c r="B39" s="138"/>
       <c r="C39" s="63"/>
-      <c r="D39" s="185">
+      <c r="D39" s="92">
         <v>102500</v>
       </c>
       <c r="E39" s="93"/>
     </row>
-    <row r="40" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="63" t="s">
         <v>120</v>
       </c>
       <c r="B40" s="63"/>
       <c r="C40" s="63"/>
-      <c r="D40" s="185">
+      <c r="D40" s="92">
         <v>36480.69</v>
       </c>
       <c r="E40" s="93"/>
     </row>
-    <row r="41" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="240" t="s">
+    <row r="41" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="240"/>
+      <c r="B41" s="196"/>
       <c r="C41" s="63"/>
-      <c r="D41" s="185">
+      <c r="D41" s="92">
         <v>29600</v>
       </c>
       <c r="E41" s="93"/>
     </row>
-    <row r="42" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="240" t="s">
+    <row r="42" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="196" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="240"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="63"/>
-      <c r="D42" s="185">
+      <c r="D42" s="92">
         <v>160000</v>
       </c>
       <c r="E42" s="93"/>
     </row>
-    <row r="43" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="240" t="s">
+    <row r="43" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="240"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="63"/>
-      <c r="D43" s="185">
+      <c r="D43" s="92">
         <v>280000</v>
       </c>
       <c r="E43" s="93"/>
     </row>
-    <row r="44" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="240" t="s">
+    <row r="44" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="240"/>
+      <c r="B44" s="196"/>
       <c r="C44" s="63"/>
-      <c r="D44" s="185">
+      <c r="D44" s="92">
         <v>215000</v>
       </c>
       <c r="E44" s="93"/>
     </row>
-    <row r="45" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="194" t="s">
+    <row r="45" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="236" t="s">
         <v>125</v>
       </c>
-      <c r="B45" s="195"/>
+      <c r="B45" s="237"/>
       <c r="C45" s="63"/>
-      <c r="D45" s="185">
+      <c r="D45" s="92">
         <v>31939.11</v>
       </c>
       <c r="E45" s="93"/>
     </row>
-    <row r="46" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="241" t="s">
+    <row r="46" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="241"/>
+      <c r="B46" s="197"/>
       <c r="C46" s="63"/>
-      <c r="D46" s="185">
+      <c r="D46" s="92">
         <v>14500</v>
       </c>
       <c r="E46" s="93"/>
     </row>
-    <row r="47" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="63" t="s">
         <v>127</v>
       </c>
       <c r="B47" s="63"/>
       <c r="C47" s="63"/>
-      <c r="D47" s="185">
+      <c r="D47" s="92">
         <v>75000</v>
       </c>
       <c r="E47" s="93"/>
     </row>
-    <row r="48" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="63" t="s">
         <v>128</v>
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="63"/>
-      <c r="D48" s="185">
+      <c r="D48" s="92">
         <v>200000</v>
       </c>
       <c r="E48" s="93"/>
     </row>
-    <row r="49" spans="1:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="63" t="s">
         <v>129</v>
       </c>
       <c r="B49" s="63"/>
       <c r="C49" s="63"/>
-      <c r="D49" s="190">
+      <c r="D49" s="66">
         <v>240000</v>
       </c>
       <c r="E49" s="93"/>
     </row>
-    <row r="50" spans="1:7" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="194"/>
-      <c r="B50" s="195"/>
+    <row r="50" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="236"/>
+      <c r="B50" s="237"/>
       <c r="C50" s="63"/>
-      <c r="D50" s="190"/>
+      <c r="D50" s="66"/>
       <c r="E50" s="93"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="139" t="s">
         <v>5</v>
       </c>
@@ -2585,7 +2619,7 @@
         <v>1385019.7999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="140" t="s">
         <v>9</v>
       </c>
@@ -2594,29 +2628,29 @@
       <c r="D52" s="95"/>
       <c r="E52" s="131"/>
     </row>
-    <row r="53" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="194" t="s">
+    <row r="53" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="236" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="195"/>
+      <c r="B53" s="237"/>
       <c r="C53" s="138"/>
-      <c r="D53" s="188">
+      <c r="D53" s="280">
         <v>209000</v>
       </c>
       <c r="E53" s="132"/>
     </row>
-    <row r="54" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="187" t="s">
+    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="185" t="s">
         <v>130</v>
       </c>
       <c r="B54" s="145"/>
       <c r="C54" s="138"/>
-      <c r="D54" s="188">
+      <c r="D54" s="280">
         <v>50000</v>
       </c>
       <c r="E54" s="132"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="139" t="s">
         <v>7</v>
       </c>
@@ -2628,7 +2662,7 @@
         <v>259000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="140" t="s">
         <v>144</v>
       </c>
@@ -2637,29 +2671,29 @@
       <c r="D56" s="169"/>
       <c r="E56" s="98"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="63" t="s">
         <v>41</v>
       </c>
       <c r="B57" s="63"/>
       <c r="C57" s="63"/>
-      <c r="D57" s="185">
+      <c r="D57" s="92">
         <v>0</v>
       </c>
       <c r="E57" s="133"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="63" t="s">
         <v>32</v>
       </c>
       <c r="B58" s="63"/>
       <c r="C58" s="63"/>
-      <c r="D58" s="185">
+      <c r="D58" s="92">
         <v>0</v>
       </c>
       <c r="E58" s="134"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="147" t="s">
         <v>7</v>
       </c>
@@ -2671,14 +2705,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="63"/>
       <c r="B60" s="63"/>
       <c r="C60" s="63"/>
       <c r="D60" s="63"/>
       <c r="E60" s="68"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="148" t="s">
         <v>150</v>
       </c>
@@ -2689,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="149"/>
       <c r="B62" s="70"/>
       <c r="C62" s="70"/>
@@ -2697,7 +2731,7 @@
       <c r="E62" s="71"/>
       <c r="F62" s="27"/>
     </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="150" t="s">
         <v>151</v>
       </c>
@@ -2711,14 +2745,14 @@
       <c r="F63" s="89"/>
       <c r="G63" s="27"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="70"/>
       <c r="B64" s="70"/>
       <c r="C64" s="70"/>
       <c r="D64" s="70"/>
       <c r="E64" s="70"/>
     </row>
-    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="70"/>
       <c r="B65" s="70"/>
       <c r="C65" s="70"/>
@@ -2726,7 +2760,7 @@
       <c r="E65" s="70"/>
       <c r="H65" s="96"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="152" t="s">
         <v>143</v>
       </c>
@@ -2735,7 +2769,7 @@
       <c r="D66" s="74"/>
       <c r="E66" s="75"/>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="155" t="s">
         <v>142</v>
       </c>
@@ -2747,42 +2781,42 @@
       </c>
       <c r="E67" s="64"/>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="193"/>
-      <c r="B68" s="193"/>
+    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="244"/>
+      <c r="B68" s="244"/>
       <c r="C68" s="63"/>
       <c r="D68" s="92"/>
       <c r="E68" s="64"/>
     </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="65"/>
       <c r="B70" s="67"/>
       <c r="C70" s="4"/>
       <c r="D70" s="66"/>
       <c r="E70" s="64"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="147" t="s">
         <v>7</v>
       </c>
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
       <c r="D71" s="35"/>
-      <c r="E71" s="247">
+      <c r="E71" s="203">
         <f>SUM(D67:D70)</f>
         <v>867931.15999999992</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
         <v>145</v>
       </c>
@@ -2791,8 +2825,8 @@
       <c r="D74" s="21"/>
       <c r="E74" s="125"/>
     </row>
-    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>146</v>
       </c>
@@ -2804,91 +2838,91 @@
         <v>867931.15999999992</v>
       </c>
     </row>
-    <row r="77" spans="1:8" s="80" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="250"/>
-      <c r="B77" s="251"/>
-      <c r="C77" s="250"/>
-      <c r="D77" s="250"/>
-      <c r="E77" s="252"/>
-    </row>
-    <row r="78" spans="1:8" s="80" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="253" t="s">
+    <row r="77" spans="1:8" s="80" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="206"/>
+      <c r="B77" s="207"/>
+      <c r="C77" s="206"/>
+      <c r="D77" s="206"/>
+      <c r="E77" s="208"/>
+    </row>
+    <row r="78" spans="1:8" s="80" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="209" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="254"/>
-      <c r="C78" s="255"/>
-      <c r="D78" s="254"/>
-      <c r="E78" s="256"/>
-    </row>
-    <row r="79" spans="1:8" s="80" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="196" t="s">
+      <c r="B78" s="210"/>
+      <c r="C78" s="211"/>
+      <c r="D78" s="210"/>
+      <c r="E78" s="212"/>
+    </row>
+    <row r="79" spans="1:8" s="80" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="245" t="s">
         <v>161</v>
       </c>
-      <c r="B79" s="197"/>
+      <c r="B79" s="246"/>
       <c r="C79" s="63"/>
       <c r="D79" s="92">
         <v>160000</v>
       </c>
       <c r="E79" s="64"/>
     </row>
-    <row r="80" spans="1:8" s="80" customFormat="1" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="193" t="s">
+    <row r="80" spans="1:8" s="80" customFormat="1" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="244" t="s">
         <v>162</v>
       </c>
-      <c r="B80" s="193"/>
+      <c r="B80" s="244"/>
       <c r="C80" s="63"/>
       <c r="D80" s="92">
         <v>2591824.4500000002</v>
       </c>
       <c r="E80" s="64"/>
     </row>
-    <row r="81" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
     </row>
-    <row r="82" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="65"/>
       <c r="B82" s="67"/>
       <c r="C82" s="4"/>
       <c r="D82" s="66"/>
       <c r="E82" s="64"/>
     </row>
-    <row r="83" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="147" t="s">
         <v>7</v>
       </c>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
       <c r="D83" s="35"/>
-      <c r="E83" s="247">
+      <c r="E83" s="203">
         <f>SUM(D79:D82)</f>
         <v>2751824.45</v>
       </c>
     </row>
-    <row r="84" spans="1:5" s="80" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" s="80" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84"/>
       <c r="B84"/>
       <c r="C84"/>
       <c r="D84"/>
       <c r="E84"/>
     </row>
-    <row r="85" spans="1:5" s="80" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="257" t="s">
+    <row r="85" spans="1:5" s="80" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="213" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="258"/>
-      <c r="C85" s="259"/>
-      <c r="D85" s="259"/>
-      <c r="E85" s="260">
+      <c r="B85" s="214"/>
+      <c r="C85" s="215"/>
+      <c r="D85" s="215"/>
+      <c r="E85" s="216">
         <f>E83</f>
         <v>2751824.45</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="61" t="s">
         <v>152</v>
       </c>
@@ -2897,7 +2931,7 @@
         <v>3865183.9699999997</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="61" t="s">
         <v>153</v>
       </c>
@@ -2906,7 +2940,7 @@
         <v>3865183.9699999997</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="61" t="s">
         <v>147</v>
       </c>
@@ -2915,8 +2949,8 @@
         <v>867931.15999999992</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="248" t="s">
+    <row r="90" spans="1:5" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="204" t="s">
         <v>148</v>
       </c>
       <c r="B90" s="62">
@@ -2924,12 +2958,12 @@
         <v>867931.15999999992</v>
       </c>
     </row>
-    <row r="92" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92" s="26"/>
       <c r="C92" s="24"/>
     </row>
-    <row r="93" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="82" t="s">
         <v>52</v>
       </c>
@@ -2939,37 +2973,37 @@
       <c r="C93" s="24"/>
       <c r="D93" s="30"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="B94" s="249">
+      <c r="B94" s="205">
         <f>-B88</f>
         <v>-3865183.9699999997</v>
       </c>
       <c r="E94" s="27"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="B95" s="249">
+      <c r="B95" s="205">
         <f>-B89</f>
         <v>-867931.15999999992</v>
       </c>
       <c r="E95" s="27"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B96" s="249">
+      <c r="B96" s="205">
         <f>-E85</f>
         <v>-2751824.45</v>
       </c>
       <c r="E96" s="27"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
         <v>53</v>
       </c>
@@ -2979,7 +3013,7 @@
       </c>
       <c r="E97" s="27"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
         <v>21</v>
       </c>
@@ -2988,7 +3022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
         <v>157</v>
       </c>
@@ -2996,7 +3030,7 @@
         <v>154086</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
         <v>158</v>
       </c>
@@ -3004,11 +3038,11 @@
         <v>63214</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="34"/>
       <c r="B101" s="88"/>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="85" t="s">
         <v>169</v>
       </c>
@@ -3017,47 +3051,47 @@
         <v>-838352.51691284962</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="83"/>
       <c r="B103" s="83"/>
       <c r="E103" s="26"/>
     </row>
-    <row r="104" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="278" t="s">
+    <row r="104" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="247" t="s">
         <v>170</v>
       </c>
-      <c r="B104" s="279"/>
-      <c r="C104" s="282"/>
+      <c r="B104" s="248"/>
+      <c r="C104" s="234"/>
       <c r="E104" s="26"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="280"/>
-      <c r="B105" s="281"/>
-      <c r="C105" s="283"/>
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="249"/>
+      <c r="B105" s="250"/>
+      <c r="C105" s="235"/>
       <c r="E105" s="26"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="83"/>
       <c r="B106" s="83"/>
       <c r="E106" s="26"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="83"/>
       <c r="B107" s="83"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="192" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="243" t="s">
         <v>16</v>
       </c>
-      <c r="B108" s="192"/>
-      <c r="C108" s="192"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="192"/>
-      <c r="B109" s="192"/>
-      <c r="C109" s="192"/>
-    </row>
-    <row r="110" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="243"/>
+      <c r="C108" s="243"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="243"/>
+      <c r="B109" s="243"/>
+      <c r="C109" s="243"/>
+    </row>
+    <row r="110" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="77"/>
       <c r="B110" s="23"/>
       <c r="C110" s="23">
@@ -3065,13 +3099,13 @@
       </c>
       <c r="E110" s="89"/>
     </row>
-    <row r="111" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="77"/>
       <c r="B111" s="79"/>
       <c r="C111" s="76"/>
       <c r="D111" s="89"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
         <v>5</v>
       </c>
@@ -3081,44 +3115,39 @@
       </c>
       <c r="C112" s="29"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M113" s="5"/>
     </row>
-    <row r="114" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="191"/>
-      <c r="B114" s="191"/>
-      <c r="C114" s="191"/>
-      <c r="D114" s="191"/>
-      <c r="E114" s="191"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="191"/>
-      <c r="B115" s="191"/>
-      <c r="C115" s="191"/>
-      <c r="D115" s="191"/>
-      <c r="E115" s="191"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="191"/>
-      <c r="B116" s="191"/>
-      <c r="C116" s="191"/>
-      <c r="D116" s="191"/>
-      <c r="E116" s="191"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="191"/>
-      <c r="B117" s="191"/>
-      <c r="C117" s="191"/>
-      <c r="D117" s="191"/>
-      <c r="E117" s="191"/>
+    <row r="114" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="242"/>
+      <c r="B114" s="242"/>
+      <c r="C114" s="242"/>
+      <c r="D114" s="242"/>
+      <c r="E114" s="242"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="242"/>
+      <c r="B115" s="242"/>
+      <c r="C115" s="242"/>
+      <c r="D115" s="242"/>
+      <c r="E115" s="242"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="242"/>
+      <c r="B116" s="242"/>
+      <c r="C116" s="242"/>
+      <c r="D116" s="242"/>
+      <c r="E116" s="242"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="242"/>
+      <c r="B117" s="242"/>
+      <c r="C117" s="242"/>
+      <c r="D117" s="242"/>
+      <c r="E117" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A114:E117"/>
     <mergeCell ref="A108:C109"/>
@@ -3129,6 +3158,11 @@
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A104:B105"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3139,46 +3173,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="105"/>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
-      <c r="M1" s="207"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
+      <c r="G1" s="251"/>
+      <c r="H1" s="251"/>
+      <c r="I1" s="251"/>
+      <c r="J1" s="251"/>
+      <c r="K1" s="251"/>
+      <c r="L1" s="251"/>
+      <c r="M1" s="251"/>
       <c r="N1" s="106"/>
       <c r="O1" s="108"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="109"/>
       <c r="B2" s="110"/>
       <c r="C2" s="111"/>
@@ -3204,7 +3238,7 @@
       <c r="O2" s="116"/>
       <c r="P2" s="19"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109"/>
       <c r="B3" s="110"/>
       <c r="C3" s="111"/>
@@ -3222,7 +3256,7 @@
       <c r="O3" s="116"/>
       <c r="P3" s="19"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="109"/>
       <c r="B4" s="110"/>
       <c r="C4" s="111"/>
@@ -3249,7 +3283,7 @@
       <c r="O4" s="116"/>
       <c r="P4" s="19"/>
     </row>
-    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="109"/>
       <c r="B5" s="110"/>
       <c r="C5" s="110"/>
@@ -3267,203 +3301,203 @@
       <c r="O5" s="116"/>
       <c r="P5" s="19"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="260" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="213"/>
-      <c r="H6" s="213"/>
-      <c r="I6" s="213"/>
-      <c r="J6" s="213"/>
-      <c r="K6" s="213"/>
-      <c r="L6" s="213"/>
-      <c r="M6" s="213"/>
-      <c r="N6" s="213"/>
-      <c r="O6" s="214"/>
+      <c r="B6" s="261"/>
+      <c r="C6" s="261"/>
+      <c r="D6" s="261"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
+      <c r="H6" s="261"/>
+      <c r="I6" s="261"/>
+      <c r="J6" s="261"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="261"/>
+      <c r="M6" s="261"/>
+      <c r="N6" s="261"/>
+      <c r="O6" s="262"/>
       <c r="P6" s="19"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="217"/>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="263"/>
+      <c r="B7" s="264"/>
+      <c r="C7" s="264"/>
+      <c r="D7" s="264"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
+      <c r="G7" s="264"/>
+      <c r="H7" s="264"/>
+      <c r="I7" s="264"/>
+      <c r="J7" s="264"/>
+      <c r="K7" s="264"/>
+      <c r="L7" s="264"/>
+      <c r="M7" s="264"/>
+      <c r="N7" s="264"/>
+      <c r="O7" s="265"/>
       <c r="P7" s="19"/>
     </row>
-    <row r="8" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="215"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="216"/>
-      <c r="O8" s="217"/>
+    <row r="8" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="263"/>
+      <c r="B8" s="264"/>
+      <c r="C8" s="264"/>
+      <c r="D8" s="264"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="264"/>
+      <c r="I8" s="264"/>
+      <c r="J8" s="264"/>
+      <c r="K8" s="264"/>
+      <c r="L8" s="264"/>
+      <c r="M8" s="264"/>
+      <c r="N8" s="264"/>
+      <c r="O8" s="265"/>
       <c r="P8" s="19"/>
     </row>
-    <row r="9" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="215"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="216"/>
-      <c r="I9" s="216"/>
-      <c r="J9" s="216"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
-      <c r="M9" s="216"/>
-      <c r="N9" s="216"/>
-      <c r="O9" s="217"/>
+    <row r="9" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="263"/>
+      <c r="B9" s="264"/>
+      <c r="C9" s="264"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
+      <c r="M9" s="264"/>
+      <c r="N9" s="264"/>
+      <c r="O9" s="265"/>
       <c r="P9" s="19"/>
     </row>
-    <row r="10" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="218"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
-      <c r="D10" s="219"/>
-      <c r="E10" s="219"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="219"/>
-      <c r="I10" s="219"/>
-      <c r="J10" s="219"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="219"/>
-      <c r="N10" s="219"/>
-      <c r="O10" s="220"/>
-    </row>
-    <row r="11" spans="1:16" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="223" t="s">
+    <row r="10" spans="1:16" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="266"/>
+      <c r="B10" s="267"/>
+      <c r="C10" s="267"/>
+      <c r="D10" s="267"/>
+      <c r="E10" s="267"/>
+      <c r="F10" s="267"/>
+      <c r="G10" s="267"/>
+      <c r="H10" s="267"/>
+      <c r="I10" s="267"/>
+      <c r="J10" s="267"/>
+      <c r="K10" s="267"/>
+      <c r="L10" s="267"/>
+      <c r="M10" s="267"/>
+      <c r="N10" s="267"/>
+      <c r="O10" s="268"/>
+    </row>
+    <row r="11" spans="1:16" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="271" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="224"/>
-      <c r="C11" s="224"/>
-      <c r="D11" s="224"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="224"/>
-      <c r="G11" s="224"/>
-      <c r="H11" s="224"/>
-      <c r="I11" s="224"/>
-      <c r="J11" s="224"/>
-      <c r="K11" s="224"/>
-      <c r="L11" s="224"/>
-      <c r="M11" s="224"/>
-      <c r="N11" s="224"/>
-      <c r="O11" s="224"/>
-    </row>
-    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="225" t="s">
+      <c r="B11" s="272"/>
+      <c r="C11" s="272"/>
+      <c r="D11" s="272"/>
+      <c r="E11" s="272"/>
+      <c r="F11" s="272"/>
+      <c r="G11" s="272"/>
+      <c r="H11" s="272"/>
+      <c r="I11" s="272"/>
+      <c r="J11" s="272"/>
+      <c r="K11" s="272"/>
+      <c r="L11" s="272"/>
+      <c r="M11" s="272"/>
+      <c r="N11" s="272"/>
+      <c r="O11" s="272"/>
+    </row>
+    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="273" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-      <c r="I12" s="225"/>
-      <c r="J12" s="225"/>
-      <c r="K12" s="225"/>
-      <c r="L12" s="225"/>
-      <c r="M12" s="225"/>
-      <c r="N12" s="225"/>
-      <c r="O12" s="225"/>
-    </row>
-    <row r="13" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="202" t="s">
+      <c r="B12" s="273"/>
+      <c r="C12" s="273"/>
+      <c r="D12" s="273"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="273"/>
+      <c r="G12" s="273"/>
+      <c r="H12" s="273"/>
+      <c r="I12" s="273"/>
+      <c r="J12" s="273"/>
+      <c r="K12" s="273"/>
+      <c r="L12" s="273"/>
+      <c r="M12" s="273"/>
+      <c r="N12" s="273"/>
+      <c r="O12" s="273"/>
+    </row>
+    <row r="13" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="256" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="202" t="s">
+      <c r="B13" s="256" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="202" t="s">
+      <c r="C13" s="256" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="202" t="s">
+      <c r="D13" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="205" t="s">
+      <c r="E13" s="252" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="202" t="s">
+      <c r="F13" s="256" t="s">
         <v>4</v>
       </c>
-      <c r="G13" s="210" t="s">
+      <c r="G13" s="258" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="205" t="s">
+      <c r="H13" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="I13" s="205" t="s">
+      <c r="I13" s="252" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="205" t="s">
+      <c r="J13" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="K13" s="205" t="s">
+      <c r="K13" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="205" t="s">
+      <c r="L13" s="252" t="s">
         <v>116</v>
       </c>
       <c r="M13" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="N13" s="208" t="s">
+      <c r="N13" s="254" t="s">
         <v>10</v>
       </c>
-      <c r="O13" s="221" t="s">
+      <c r="O13" s="269" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="203"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="211"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="206"/>
-      <c r="J14" s="206"/>
-      <c r="K14" s="206"/>
-      <c r="L14" s="206"/>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="274"/>
+      <c r="B14" s="257"/>
+      <c r="C14" s="274"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="253"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="259"/>
+      <c r="H14" s="253"/>
+      <c r="I14" s="253"/>
+      <c r="J14" s="253"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
       <c r="M14" s="36" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 09/10</v>
       </c>
-      <c r="N14" s="209"/>
-      <c r="O14" s="222"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="255"/>
+      <c r="O14" s="270"/>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
         <v>54</v>
       </c>
@@ -3473,7 +3507,7 @@
       <c r="C15" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="231">
+      <c r="D15" s="187">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="E15" s="47">
@@ -3522,7 +3556,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="118" t="s">
         <v>56</v>
       </c>
@@ -3530,7 +3564,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="119"/>
-      <c r="D16" s="232">
+      <c r="D16" s="188">
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="E16" s="48">
@@ -3580,7 +3614,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>58</v>
       </c>
@@ -3590,7 +3624,7 @@
       <c r="C17" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="231">
+      <c r="D17" s="187">
         <v>4.82E-2</v>
       </c>
       <c r="E17" s="47">
@@ -3640,56 +3674,56 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="271" t="s">
+    <row r="18" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="227" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="271" t="s">
+      <c r="B18" s="227" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="272" t="s">
+      <c r="C18" s="228" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="273">
+      <c r="D18" s="229">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="E18" s="263">
+      <c r="E18" s="219">
         <v>6715695.8885622956</v>
       </c>
-      <c r="F18" s="263"/>
-      <c r="G18" s="274">
+      <c r="F18" s="219"/>
+      <c r="G18" s="230">
         <f t="shared" si="0"/>
         <v>6715695.8885622956</v>
       </c>
-      <c r="H18" s="274">
+      <c r="H18" s="230">
         <f t="shared" si="1"/>
         <v>248480.74787680496</v>
       </c>
-      <c r="I18" s="275">
+      <c r="I18" s="231">
         <f t="shared" si="2"/>
         <v>46434.317059999994</v>
       </c>
-      <c r="J18" s="275">
+      <c r="J18" s="231">
         <f t="shared" si="3"/>
         <v>206787.34239499999</v>
       </c>
-      <c r="K18" s="276">
+      <c r="K18" s="232">
         <f t="shared" si="4"/>
         <v>9043.8004999999994</v>
       </c>
-      <c r="L18" s="268">
+      <c r="L18" s="224">
         <f t="shared" si="5"/>
         <v>23110.395</v>
       </c>
-      <c r="M18" s="268">
+      <c r="M18" s="224">
         <f t="shared" si="6"/>
         <v>7249552.04</v>
       </c>
-      <c r="N18" s="269">
+      <c r="N18" s="225">
         <f t="shared" si="7"/>
         <v>7684525.04</v>
       </c>
-      <c r="O18" s="270">
+      <c r="O18" s="226">
         <f t="shared" si="8"/>
         <v>7467039.04</v>
       </c>
@@ -3698,7 +3732,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="118" t="s">
         <v>62</v>
       </c>
@@ -3706,7 +3740,7 @@
         <v>63</v>
       </c>
       <c r="C19" s="118"/>
-      <c r="D19" s="232">
+      <c r="D19" s="188">
         <v>3.85E-2</v>
       </c>
       <c r="E19" s="48">
@@ -3756,7 +3790,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
         <v>64</v>
       </c>
@@ -3764,7 +3798,7 @@
         <v>65</v>
       </c>
       <c r="C20" s="39"/>
-      <c r="D20" s="232">
+      <c r="D20" s="188">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="E20" s="47">
@@ -3814,7 +3848,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="118" t="s">
         <v>66</v>
       </c>
@@ -3822,7 +3856,7 @@
         <v>67</v>
       </c>
       <c r="C21" s="118"/>
-      <c r="D21" s="232">
+      <c r="D21" s="188">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="E21" s="48">
@@ -3872,7 +3906,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="118" t="s">
         <v>68</v>
       </c>
@@ -3882,7 +3916,7 @@
       <c r="C22" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="232">
+      <c r="D22" s="188">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="E22" s="48">
@@ -3932,7 +3966,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="118" t="s">
         <v>70</v>
       </c>
@@ -3942,7 +3976,7 @@
       <c r="C23" s="119" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="232">
+      <c r="D23" s="188">
         <v>3.85E-2</v>
       </c>
       <c r="E23" s="47">
@@ -3992,7 +4026,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="118" t="s">
         <v>72</v>
       </c>
@@ -4000,7 +4034,7 @@
         <v>73</v>
       </c>
       <c r="C24" s="119"/>
-      <c r="D24" s="231">
+      <c r="D24" s="187">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="E24" s="47">
@@ -4048,56 +4082,56 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="261" t="s">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="217" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="261" t="s">
+      <c r="B25" s="217" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="262" t="s">
+      <c r="C25" s="218" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="233">
+      <c r="D25" s="189">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E25" s="263">
+      <c r="E25" s="219">
         <v>4792208.6425903365</v>
       </c>
-      <c r="F25" s="263"/>
-      <c r="G25" s="264">
+      <c r="F25" s="219"/>
+      <c r="G25" s="220">
         <f t="shared" si="0"/>
         <v>4792208.6425903365</v>
       </c>
-      <c r="H25" s="264">
+      <c r="H25" s="220">
         <f t="shared" si="1"/>
         <v>177311.71977584247</v>
       </c>
-      <c r="I25" s="265">
+      <c r="I25" s="221">
         <f t="shared" si="2"/>
         <v>35932.350023999999</v>
       </c>
-      <c r="J25" s="265">
+      <c r="J25" s="221">
         <f t="shared" si="3"/>
         <v>160018.616358</v>
       </c>
-      <c r="K25" s="266">
+      <c r="K25" s="222">
         <f t="shared" si="4"/>
         <v>6998.3801999999996</v>
       </c>
-      <c r="L25" s="267">
+      <c r="L25" s="223">
         <f t="shared" si="5"/>
         <v>17883.558000000001</v>
       </c>
-      <c r="M25" s="268">
+      <c r="M25" s="224">
         <f t="shared" si="6"/>
         <v>5190353.1100000003</v>
       </c>
-      <c r="N25" s="269">
+      <c r="N25" s="225">
         <f t="shared" si="7"/>
         <v>5501774.1100000003</v>
       </c>
-      <c r="O25" s="270">
+      <c r="O25" s="226">
         <f t="shared" si="8"/>
         <v>5346064.1100000003</v>
       </c>
@@ -4106,7 +4140,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>76</v>
       </c>
@@ -4116,7 +4150,7 @@
       <c r="C26" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="234">
+      <c r="D26" s="190">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="E26" s="47">
@@ -4166,56 +4200,56 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="261" t="s">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="217" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="261" t="s">
+      <c r="B27" s="217" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="262"/>
-      <c r="D27" s="235">
+      <c r="C27" s="218"/>
+      <c r="D27" s="191">
         <v>3.85E-2</v>
       </c>
-      <c r="E27" s="263">
+      <c r="E27" s="219">
         <v>2359047.9860918703</v>
       </c>
-      <c r="F27" s="263">
-        <v>0</v>
-      </c>
-      <c r="G27" s="264">
+      <c r="F27" s="219">
+        <v>0</v>
+      </c>
+      <c r="G27" s="220">
         <f t="shared" si="0"/>
         <v>2359047.9860918703</v>
       </c>
-      <c r="H27" s="264">
+      <c r="H27" s="220">
         <f t="shared" si="1"/>
         <v>87284.775485399208</v>
       </c>
-      <c r="I27" s="265">
+      <c r="I27" s="221">
         <f t="shared" si="2"/>
         <v>33415.34966</v>
       </c>
-      <c r="J27" s="265">
+      <c r="J27" s="221">
         <f t="shared" si="3"/>
         <v>148809.582845</v>
       </c>
-      <c r="K27" s="266">
+      <c r="K27" s="222">
         <f t="shared" si="4"/>
         <v>6508.1554999999998</v>
       </c>
-      <c r="L27" s="267">
+      <c r="L27" s="223">
         <f t="shared" si="5"/>
         <v>16630.845000000001</v>
       </c>
-      <c r="M27" s="268">
+      <c r="M27" s="224">
         <f t="shared" si="6"/>
         <v>2651697.13</v>
       </c>
-      <c r="N27" s="269">
+      <c r="N27" s="225">
         <f t="shared" si="7"/>
         <v>2810799.13</v>
       </c>
-      <c r="O27" s="270">
+      <c r="O27" s="226">
         <f t="shared" si="8"/>
         <v>2731248.13</v>
       </c>
@@ -4224,7 +4258,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="118" t="s">
         <v>80</v>
       </c>
@@ -4234,7 +4268,7 @@
       <c r="C28" s="119" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="236">
+      <c r="D28" s="192">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="E28" s="48">
@@ -4284,7 +4318,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39" t="s">
         <v>82</v>
       </c>
@@ -4294,7 +4328,7 @@
       <c r="C29" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="237">
+      <c r="D29" s="193">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="E29" s="47">
@@ -4344,7 +4378,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="118" t="s">
         <v>84</v>
       </c>
@@ -4352,7 +4386,7 @@
         <v>85</v>
       </c>
       <c r="C30" s="39"/>
-      <c r="D30" s="238">
+      <c r="D30" s="194">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="E30" s="47">
@@ -4402,7 +4436,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="118" t="s">
         <v>86</v>
       </c>
@@ -4412,7 +4446,7 @@
       <c r="C31" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="238">
+      <c r="D31" s="194">
         <v>3.85E-2</v>
       </c>
       <c r="E31" s="48">
@@ -4462,7 +4496,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
         <v>88</v>
       </c>
@@ -4470,7 +4504,7 @@
         <v>89</v>
       </c>
       <c r="C32" s="81"/>
-      <c r="D32" s="238">
+      <c r="D32" s="194">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="E32" s="47">
@@ -4520,55 +4554,55 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="261" t="s">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="217" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="261" t="s">
+      <c r="B33" s="217" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="262" t="s">
+      <c r="C33" s="218" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="239">
+      <c r="D33" s="195">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="E33" s="263">
+      <c r="E33" s="219">
         <v>3935634.9310685159</v>
       </c>
-      <c r="F33" s="263">
+      <c r="F33" s="219">
         <v>125922.6</v>
       </c>
-      <c r="G33" s="264">
+      <c r="G33" s="220">
         <f t="shared" si="0"/>
         <v>3809712.3310685158</v>
       </c>
-      <c r="H33" s="264">
+      <c r="H33" s="220">
         <f t="shared" si="1"/>
         <v>140959.35624953511</v>
       </c>
-      <c r="I33" s="265">
+      <c r="I33" s="221">
         <f t="shared" si="2"/>
         <v>35932.350023999999</v>
       </c>
-      <c r="J33" s="265">
+      <c r="J33" s="221">
         <f t="shared" si="3"/>
         <v>160018.616358</v>
       </c>
-      <c r="K33" s="266">
+      <c r="K33" s="222">
         <f t="shared" si="4"/>
         <v>6998.3801999999996</v>
       </c>
-      <c r="L33" s="267">
+      <c r="L33" s="223">
         <f t="shared" si="5"/>
         <v>17883.558000000001</v>
       </c>
-      <c r="M33" s="268">
+      <c r="M33" s="224">
         <f t="shared" si="6"/>
         <v>4171505.19</v>
       </c>
-      <c r="N33" s="269"/>
-      <c r="O33" s="270">
+      <c r="N33" s="225"/>
+      <c r="O33" s="226">
         <f t="shared" si="8"/>
         <v>4296650.1899999995</v>
       </c>
@@ -4577,7 +4611,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
         <v>92</v>
       </c>
@@ -4585,7 +4619,7 @@
         <v>93</v>
       </c>
       <c r="C34" s="40"/>
-      <c r="D34" s="238">
+      <c r="D34" s="194">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="E34" s="54">
@@ -4629,7 +4663,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A35" s="52" t="s">
         <v>94</v>
       </c>
@@ -4639,7 +4673,7 @@
       <c r="C35" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="238">
+      <c r="D35" s="194">
         <v>3.85E-2</v>
       </c>
       <c r="E35" s="54">
@@ -4686,7 +4720,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="53" t="s">
         <v>96</v>
       </c>
@@ -4696,13 +4730,13 @@
       <c r="C36" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="238">
+      <c r="D36" s="194">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="E36" s="54">
         <v>109193.585395</v>
       </c>
-      <c r="F36" s="277">
+      <c r="F36" s="233">
         <v>109193.585395</v>
       </c>
       <c r="G36" s="49">
@@ -4743,7 +4777,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="55" t="s">
         <v>98</v>
       </c>
@@ -4751,7 +4785,7 @@
         <v>99</v>
       </c>
       <c r="C37" s="40"/>
-      <c r="D37" s="238">
+      <c r="D37" s="194">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="E37" s="54">
@@ -4798,7 +4832,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="57"/>
       <c r="B38" s="58"/>
       <c r="C38" s="58"/>
@@ -4851,100 +4885,105 @@
         <v>28602633.759999998</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="191" t="str">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="242" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="C41" s="191"/>
-      <c r="D41" s="191"/>
-      <c r="E41" s="191"/>
-      <c r="F41" s="191"/>
-      <c r="G41" s="191"/>
-      <c r="H41" s="191"/>
-      <c r="I41" s="191"/>
-      <c r="J41" s="191"/>
-      <c r="K41" s="191"/>
-      <c r="L41" s="191"/>
-      <c r="M41" s="191"/>
-    </row>
-    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="191"/>
-      <c r="C42" s="191"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="191"/>
-      <c r="F42" s="191"/>
-      <c r="G42" s="191"/>
-      <c r="H42" s="191"/>
-      <c r="I42" s="191"/>
-      <c r="J42" s="191"/>
-      <c r="K42" s="191"/>
-      <c r="L42" s="191"/>
-      <c r="M42" s="191"/>
-    </row>
-    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="191"/>
-      <c r="C43" s="191"/>
-      <c r="D43" s="191"/>
-      <c r="E43" s="191"/>
-      <c r="F43" s="191"/>
-      <c r="G43" s="191"/>
-      <c r="H43" s="191"/>
-      <c r="I43" s="191"/>
-      <c r="J43" s="191"/>
-      <c r="K43" s="191"/>
-      <c r="L43" s="191"/>
-      <c r="M43" s="191"/>
-    </row>
-    <row r="44" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="191"/>
-      <c r="C44" s="191"/>
-      <c r="D44" s="191"/>
-      <c r="E44" s="191"/>
-      <c r="F44" s="191"/>
-      <c r="G44" s="191"/>
-      <c r="H44" s="191"/>
-      <c r="I44" s="191"/>
-      <c r="J44" s="191"/>
-      <c r="K44" s="191"/>
-      <c r="L44" s="191"/>
-      <c r="M44" s="191"/>
-    </row>
-    <row r="45" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="191"/>
-      <c r="C45" s="191"/>
-      <c r="D45" s="191"/>
-      <c r="E45" s="191"/>
-      <c r="F45" s="191"/>
-      <c r="G45" s="191"/>
-      <c r="H45" s="191"/>
-      <c r="I45" s="191"/>
-      <c r="J45" s="191"/>
-      <c r="K45" s="191"/>
-      <c r="L45" s="191"/>
-      <c r="M45" s="191"/>
-    </row>
-    <row r="46" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="191"/>
-      <c r="C46" s="191"/>
-      <c r="D46" s="191"/>
-      <c r="E46" s="191"/>
-      <c r="F46" s="191"/>
-      <c r="G46" s="191"/>
-      <c r="H46" s="191"/>
-      <c r="I46" s="191"/>
-      <c r="J46" s="191"/>
-      <c r="K46" s="191"/>
-      <c r="L46" s="191"/>
-      <c r="M46" s="191"/>
+      <c r="C41" s="242"/>
+      <c r="D41" s="242"/>
+      <c r="E41" s="242"/>
+      <c r="F41" s="242"/>
+      <c r="G41" s="242"/>
+      <c r="H41" s="242"/>
+      <c r="I41" s="242"/>
+      <c r="J41" s="242"/>
+      <c r="K41" s="242"/>
+      <c r="L41" s="242"/>
+      <c r="M41" s="242"/>
+    </row>
+    <row r="42" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="242"/>
+      <c r="C42" s="242"/>
+      <c r="D42" s="242"/>
+      <c r="E42" s="242"/>
+      <c r="F42" s="242"/>
+      <c r="G42" s="242"/>
+      <c r="H42" s="242"/>
+      <c r="I42" s="242"/>
+      <c r="J42" s="242"/>
+      <c r="K42" s="242"/>
+      <c r="L42" s="242"/>
+      <c r="M42" s="242"/>
+    </row>
+    <row r="43" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="242"/>
+      <c r="C43" s="242"/>
+      <c r="D43" s="242"/>
+      <c r="E43" s="242"/>
+      <c r="F43" s="242"/>
+      <c r="G43" s="242"/>
+      <c r="H43" s="242"/>
+      <c r="I43" s="242"/>
+      <c r="J43" s="242"/>
+      <c r="K43" s="242"/>
+      <c r="L43" s="242"/>
+      <c r="M43" s="242"/>
+    </row>
+    <row r="44" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="242"/>
+      <c r="C44" s="242"/>
+      <c r="D44" s="242"/>
+      <c r="E44" s="242"/>
+      <c r="F44" s="242"/>
+      <c r="G44" s="242"/>
+      <c r="H44" s="242"/>
+      <c r="I44" s="242"/>
+      <c r="J44" s="242"/>
+      <c r="K44" s="242"/>
+      <c r="L44" s="242"/>
+      <c r="M44" s="242"/>
+    </row>
+    <row r="45" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="242"/>
+      <c r="C45" s="242"/>
+      <c r="D45" s="242"/>
+      <c r="E45" s="242"/>
+      <c r="F45" s="242"/>
+      <c r="G45" s="242"/>
+      <c r="H45" s="242"/>
+      <c r="I45" s="242"/>
+      <c r="J45" s="242"/>
+      <c r="K45" s="242"/>
+      <c r="L45" s="242"/>
+      <c r="M45" s="242"/>
+    </row>
+    <row r="46" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="242"/>
+      <c r="C46" s="242"/>
+      <c r="D46" s="242"/>
+      <c r="E46" s="242"/>
+      <c r="F46" s="242"/>
+      <c r="G46" s="242"/>
+      <c r="H46" s="242"/>
+      <c r="I46" s="242"/>
+      <c r="J46" s="242"/>
+      <c r="K46" s="242"/>
+      <c r="L46" s="242"/>
+      <c r="M46" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B41:M46"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="L13:L14"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="E13:E14"/>
@@ -4959,11 +4998,6 @@
     <mergeCell ref="A12:O12"/>
     <mergeCell ref="K13:K14"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B41:M46"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="L13:L14"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4973,36 +5007,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E11DE44-94AC-4627-8367-E065E39D764D}">
   <dimension ref="B2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="1.88671875" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" style="102" customWidth="1"/>
-    <col min="12" max="12" width="2.109375" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" style="103" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="1.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="102" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="103" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" style="161" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="161" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="D2" s="226" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="275" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="227" t="s">
+      <c r="H2" s="276" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="228"/>
+      <c r="I2" s="277"/>
       <c r="J2" s="1"/>
       <c r="K2" s="184" t="s">
         <v>44</v>
@@ -5014,7 +5048,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="100" t="s">
         <v>24</v>
       </c>
@@ -5040,7 +5074,7 @@
       <c r="M3" s="101"/>
       <c r="O3" s="184"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="172">
         <v>1</v>
       </c>
@@ -5075,7 +5109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="100">
         <v>1</v>
       </c>
@@ -5109,7 +5143,7 @@
         <v>125263.16548665638</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="172">
         <v>1</v>
       </c>
@@ -5144,7 +5178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="172">
         <v>2</v>
       </c>
@@ -5179,7 +5213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="172">
         <v>2</v>
       </c>
@@ -5214,7 +5248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="172">
         <v>2</v>
       </c>
@@ -5249,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="172">
         <v>2</v>
       </c>
@@ -5284,7 +5318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="172">
         <v>3</v>
       </c>
@@ -5319,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="100">
         <v>3</v>
       </c>
@@ -5353,7 +5387,7 @@
         <v>98658.340164570633</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="172">
         <v>3</v>
       </c>
@@ -5388,7 +5422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="172">
         <v>3</v>
       </c>
@@ -5423,7 +5457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="172">
         <v>4</v>
       </c>
@@ -5458,7 +5492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="172">
         <v>4</v>
       </c>
@@ -5493,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="172">
         <v>4</v>
       </c>
@@ -5528,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="172">
         <v>4</v>
       </c>
@@ -5563,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="172"/>
       <c r="C19" s="172"/>
       <c r="D19" s="173"/>
@@ -5575,7 +5609,7 @@
       <c r="M19" s="101"/>
       <c r="O19" s="184"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="100"/>
       <c r="C20" s="100" t="s">
         <v>48</v>
@@ -5607,7 +5641,7 @@
         <v>223921.50565122702</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="100"/>
       <c r="C21" s="100"/>
       <c r="D21" s="4"/>
@@ -5616,7 +5650,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="100" t="s">
         <v>30</v>
       </c>
@@ -5644,7 +5678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="100" t="s">
         <v>30</v>
       </c>
@@ -5672,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="100" t="s">
         <v>30</v>
       </c>
@@ -5700,7 +5734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="100" t="s">
         <v>30</v>
       </c>
@@ -5728,7 +5762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="100" t="s">
         <v>30</v>
       </c>
@@ -5756,7 +5790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="100" t="s">
         <v>30</v>
       </c>
@@ -5784,7 +5818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="100" t="s">
         <v>30</v>
       </c>
@@ -5812,7 +5846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="100" t="s">
         <v>30</v>
       </c>
@@ -5840,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H30" s="184" t="s">
         <v>38</v>
       </c>
@@ -5848,7 +5882,7 @@
         <f>SUM(I22:I29)</f>
         <v>1903.8315368098165</v>
       </c>
-      <c r="K30" s="189">
+      <c r="K30" s="186">
         <f>SUM(K22:K29)</f>
         <v>1903.8315368098165</v>
       </c>
@@ -5861,14 +5895,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O31" s="137"/>
     </row>
-    <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D32" s="229" t="s">
+    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="278" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="230"/>
+      <c r="E32" s="279"/>
       <c r="F32" s="162">
         <v>265234.65000000002</v>
       </c>
@@ -5902,9 +5936,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" s="163" t="s">
         <v>40</v>
       </c>
